--- a/output/第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx
+++ b/output/第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_ファシリテーションの方針" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_決定①事業所実態調査" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_決定①KPI4項目の代理指標" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_決定②委員会日程" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_決定③推計の前提" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_決定④実績と点検事項" sheetId="5" state="visible" r:id="rId5"/>
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -149,6 +149,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -750,22 +753,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>決定① 事業所実態調査の実施の要否</t>
+          <t>決定① 代表KPI4項目の代理指標</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>代表KPI4項目のデータ源が決まらない。実施する場合は令和8年10月までの回収が必要。</t>
+          <t>代表KPI H07・H08・H12・H16の基準値が算定できない。追加照会を行う場合は令和8年9月中の回収が必要。</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>KPI H07・H08・H12・H16の基準値が算定できない。</t>
+          <t>代表KPIが16項目から12項目に減る可能性がある。</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>実施しない前提で代理指標案を提示し、後日ご確認いただく</t>
+          <t>代理指標を仮に置いて骨子案を進め、後日ご確認いただく</t>
         </is>
       </c>
     </row>
@@ -847,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -860,190 +863,310 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>決定① 事業所実態調査の実施の要否（ヒアリングシート 項目1）</t>
+          <t>決定① 代表KPI4項目の代理指標（ヒアリングシート 項目1）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仕様書４（3）の対象4調査に事業所実態調査・在宅介護実態調査は含まれていない。一方、キックオフ会議資料には「設計案作成済・未実施」と記載されている。実施の要否と、本業務の範囲に含むかを確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+          <t>令和8年8月6日のご連絡により、事業所実態調査は実施済みで、現時点で提出されている調査結果はすべて受領している。受領した事業所票27件の項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職であり、欠員、受入困難、休廃止・縮小意向、ICT、生産性、BCPは含まれない。このため代表KPIのH07・H08・H12・H16は基準値を算定できない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>【前提の確認（冒頭で必ず行う）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>確認すること</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>確認できた場合</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>確認できない場合</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>受領した調査結果がすべてであること</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>本シートの分岐へ進む。「受領した事業所票27件で確定」として記録する。</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>未受領の回答がある場合は、受領後に集計をやり直すことになる。受領の時期と件数を確認し、本決定を保留とする。</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>令和8年8月6日のご連絡は「現時点で提出いただいている調査結果のすべて」である。「現時点で」の含意（今後の追加提出の有無）を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>受領した事業所票の項目に、欠員・受入困難・縮小意向・ICT・BCPが含まれていないこと</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>本シートの分岐へ進む。</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>別の調査票が存在する可能性がある。調査票の版と設問一覧をご提供いただく。</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>受託者が受領した102ファイルには、在宅生活改善調査・居所変更実態調査・介護人材実態調査の3調査しか含まれていない（受領点検 01シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>【分岐】</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>分岐</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>想定される回答</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>その場での応答</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>記録・確認すること</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>後続への影響</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="11" ht="92" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>実施する。本業務の範囲に含む</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>「承知いたしました。調査票、対象事業所、実施時期、回収方法をご決定いただく必要がございます。12月の素案確定に間に合わせるには、令和8年10月までに回収を終える必要がございます。設計案をお持ちでしたら、拝見したうえで国の標準項目との対応を確認いたします。」</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>①調査票の版　②対象事業所の範囲（区域内のみか区域外を含むか）③発送・回収の主体　④実施時期　⑤督促の方法　⑥業務範囲に含む場合の契約上の扱い</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>代表KPI H12・H16の基準値が算定できる。工程に調査の実施が加わるため、10月の再基準化と並行することになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>代理指標へ振り替える（受託者の案）</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>「ありがとうございます。H12の必要サービス未充足率は、居所変更実態調査の『供給不足を理由とする住替え』に置き換えます。H16の災害・感染症時のサービス継続率は、BCPの策定率という体制の指標に組み替えます。H07・H08につきましては代替できる指標が見当たりませんので、改めてご相談させてください。」</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>①H12の代理指標　②H16の代理指標　③H07・H08の扱い　④代理指標のデータ源と更新頻度</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>骨子案 第6節、素案 第4章第3節、資料1のKPI定義を修正する。代理指標は定義が変わるため、第9期との比較はできない旨を注記する</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="92" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>実施する。ただし本業務の範囲外（広域連合が自ら実施）</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>「承知いたしました。集計・分析のみ受託者が行う形でよろしいでしょうか。その場合、集計に必要な形式で回答データをいただけますと作業が確実になります。調査票の設計段階で、KPIの分子・分母に対応する設問が含まれているかだけ確認させていただけますでしょうか。」</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>①受託者の関与範囲（集計のみか、設計の助言を含むか）②データの受渡しの時期と形式　③KPIに対応する設問の有無</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>同上。ただし調査票にKPIに対応する設問がないと基準値が算定できないため、設計段階の確認が要る</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>4項目を代表KPIから落とす</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>「承知いたしました。代表KPIは16項目から12項目となります。1点だけご留意いただきたいことがございます。H16を落としますと、基本目標5のレジリエンスに対応する成果指標がなくなります。H07・H08を落としますと、基本目標2の家族支援に対応する成果指標がなくなります。基本目標に成果指標が対応しない状態となってよいか、ご確認をお願いいたします。」</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>①落とす項目　②基本目標との対応の欠落を許容するか　③代わりに立てる指標の有無</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>代表KPIが12項目になる。基本目標2と基本目標5の達成目標（第5章（5））が空欄となる</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="92" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>実施しない</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>「承知いたしました。その場合、代表KPIの4項目について代理指標への振替をご相談させていただきます。H12の必要サービス未充足率は、居所変更実態調査の『供給不足を理由とする住替え』で部分的に代替できます。H16の災害・感染症時のサービス継続率は、BCPの策定率という体制の指標に組み替える案がございます。H07・H08は在宅介護実態調査によるもので、代替できる指標が見当たりません。この2項目を落とすか、別の指標に置き換えるかをご相談させてください。」</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>①4項目それぞれの扱い（代理指標／削除／保留）②削除する場合、基本目標との対応に欠落が生じないかの確認</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>代表KPIが16項目から12項目又は14項目に減る。骨子案 第6節、素案 第4章第3節、資料1の修正が生じる</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>事業所へ追加で照会する</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>「承知いたしました。設問を絞れば追加のご照会は可能と存じます。H12であれば『過去1年間に受け入れられなかった申込みの有無と件数』、H16であれば『BCPを策定しているか』の2問で足ります。12月の素案確定に間に合わせるには、令和8年9月中の回収が必要でございます。ご照会は広域連合様のお名前で行っていただけますでしょうか。」</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>①照会する設問　②照会の主体と経路　③回収の期限（9月中）　④督促の要否</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>9月中に回収できればH12・H16の基準値を算定できる。H07・H08は在宅介護実態調査によるため、追加照会では解決しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="92" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査を別途実施する</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>「承知いたしました。在宅介護実態調査は仕様書４（3）が定める対象4調査に含まれておりませんので、業務範囲に含めるかどうかを別途ご協議いただく必要がございます。また、実施される場合は令和8年10月までの回収が必要でございます。H07・H08のみのためにこの規模の調査を行うかどうかは、費用と工程を踏まえてご判断ください。」</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>①業務範囲に含むか　②実施時期　③調査票の設計の主体</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>工程に調査の実施が加わる。10月の再基準化と並行することになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="92" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>「設計案の項目が入っていないのはなぜか」と問われる</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>「受託者が受領いたしましたのは、在宅生活改善調査、居所変更実態調査、介護人材実態調査の3調査、102ファイルでございます。このうち事業所を対象としたものは介護人材実態調査の事業所票27件で、項目は介護職員数、常勤・非常勤、外国人、派遣、採用・離職でした。設計案の項目を含む別の調査票が存在するようでしたら、そちらをご提供いただけますでしょうか。」</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>①別の調査票の有無　②ある場合の提供時期</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>別の調査票が存在する場合は、集計をやり直す。存在しない場合は分岐A〜Dのいずれかへ進む</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="92" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>未定・持ち帰る</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>「承知いたしました。恐れ入りますが、実施される場合は令和8年10月までの回収が必要となりますので、8月中にご回答をいただけますでしょうか。それまでは、実施しない前提で代理指標の案を作成し、実施が決まった場合に差し替える形で進めてまいります。」</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>①回答の期限（8月中）　②それまでの仮置き（実施しない前提）</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>仮置きのまま進むため直ちに止まらない。ただし9月以降の決定では10月の回収に間に合わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>そもそも仕様書の範囲かどうかが論点になる</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>「仕様書４（3）が定める対象は4調査で、事業所実態調査はこの4調査に含まれておりません。受託者としては、範囲に含むかどうかをご判断いただければそれに従います。本日は範囲の判断そのものではなく、実施されるかどうかだけでもお決めいただけますと、KPIの設計を進められます。」</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>①範囲の判断を要する旨　②判断の主体と時期</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>範囲の議論に時間を取られると他の決定が処理できない。実施の要否だけ切り出す</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="96" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>注1）本件はキックオフ会議資料（更新版）で「最優先」の資料に挙げられており、発注者側で既に実施の方針がある可能性が高い。分岐AまたはBを本線として準備する。注2）分岐Eに入った場合は、範囲の議論を「後日の協議事項」として切り離し、実施の要否だけを本日の決定として持ち帰る。注3）代表KPI16項目のうち「未確保」はH07・H08・H12・H16の4項目である（骨子案 第6節）。</t>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>「承知いたしました。恐れ入りますが、追加のご照会をされる場合は令和8年9月中の回収が必要となりますので、8月中にご回答をいただけますでしょうか。それまでは、代理指標を仮に置いて骨子案を進めてまいります。」</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>①回答の期限（8月中）　②それまでの仮置き（代理指標）</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>仮置きのまま進むため直ちに止まらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="96" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>注1）本件は、キックオフ会議資料の設計案が挙げていた項目と、実際に受領した回答の項目が一致しないことによる。資料の記載を否定する言い方は避け、「受領した回答には含まれておりませんでした」と事実のみを述べる。注2）分岐Cは、2問の追加照会で2項目が解決するため費用対効果が高い。受託者としては分岐AとCの併用を勧める。注3）分岐Bを選ばれた場合は、基本目標2と基本目標5に成果指標が対応しなくなる点を必ずお伝えする。注4）H07・H08は在宅介護実態調査によるものであり、事業所への追加照会では解決しない。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1107,7 +1230,7 @@
       </c>
     </row>
     <row r="5" ht="84" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1315,7 +1438,7 @@
       </c>
     </row>
     <row r="5" ht="92" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1550,7 +1673,7 @@
       </c>
     </row>
     <row r="5" ht="92" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1577,7 +1700,7 @@
       </c>
     </row>
     <row r="6" ht="92" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -1785,7 +1908,7 @@
       </c>
     </row>
     <row r="5" ht="76" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1866,7 +1989,7 @@
       </c>
     </row>
     <row r="8" ht="76" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -1996,7 +2119,7 @@
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>「まず全体を説明してほしい」と求められる</t>
         </is>
@@ -2021,7 +2144,7 @@
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>決定権者が同席していない</t>
         </is>
@@ -2046,7 +2169,7 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>3町の担当者が同席していない</t>
         </is>
@@ -2071,7 +2194,7 @@
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>時間が押して2件以上が未処理になる</t>
         </is>
@@ -2096,7 +2219,7 @@
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>特定の論点で紛糾する</t>
         </is>
@@ -2121,7 +2244,7 @@
       <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>受託者の進捗が速いことへの懸念を示される（手戻りの心配、費用への影響等）</t>
         </is>
@@ -2146,7 +2269,7 @@
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>会議資料（更新版）の記載と食い違う点を指摘される</t>
         </is>
@@ -2171,7 +2294,7 @@
       <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>予定より早く終わりそうになる</t>
         </is>
@@ -2456,12 +2579,12 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>変更なし</t>
+          <t>実施済・回答受領済（令和8年8月6日ご連絡）</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>本日の決定①でございます。</t>
+          <t>受領した事業所票27件の項目は、介護職員数、常勤・非常勤、外国人、派遣、採用・離職でございます。設計案が挙げておられた欠員、受入困難、縮小意向、ICT、BCPは含まれておりませんでした。本日の決定①でございます。</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2709,7 @@
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>調査の結果から、どのサービスをどれだけ整備すべきか分かるのか</t>
         </is>
@@ -2606,7 +2729,7 @@
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>認定率が全国より低いのはよいことではないのか</t>
         </is>
@@ -2626,7 +2749,7 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>24時間対応のサービスは整備すべきか</t>
         </is>
@@ -2646,14 +2769,14 @@
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>介護職員は足りているのか</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>回答のあった事業所の介護職員は348人から361人でございます。勤続1年未満が19.9％、令和6年度の離職者が65人から67人で、毎年2割近くが入れ替わっている計算になります。ただし、必要人数に対して何人不足しているかという欠員の把握はできておりません。これは事業所実態調査でなければ把握できない事項でございます。</t>
+          <t>回答のあった事業所の介護職員は348人から361人でございます。勤続1年未満が19.9％、令和6年度の離職者が65人から67人で、毎年2割近くが入れ替わっている計算になります。ただし、必要人数に対して何人不足しているかという欠員の把握はできておりません。受領いたしました事業所票に欠員の設問がないためでございます。</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2666,7 +2789,7 @@
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>小規模多機能が美瑛町に偏っているのはなぜか</t>
         </is>
@@ -2686,7 +2809,7 @@
       <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>報告書に法人名を出してよいか</t>
         </is>
@@ -2706,7 +2829,7 @@
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>いつ計画書ができるのか</t>
         </is>
@@ -2726,7 +2849,7 @@
       <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>受託者の作業が先行していることで、費用は変わるのか</t>
         </is>

--- a/output/第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx
+++ b/output/第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx
@@ -2429,7 +2429,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>4調査すべて集計・分析完了。結果報告書（8章48表39図）</t>
+          <t>4調査すべて集計・分析完了。結果報告書（8章50表39図）</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">

--- a/output/第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx
+++ b/output/第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx
@@ -2429,7 +2429,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>4調査すべて集計・分析完了。結果報告書（8章50表39図）</t>
+          <t>4調査すべて集計・分析完了。結果報告書（8章51表39図）</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
